--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N68_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N68_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.67242602803879</v>
+        <v>4.334269229556304</v>
       </c>
       <c r="D2" t="n">
-        <v>26.59185125095486</v>
+        <v>4.321175828280166</v>
       </c>
       <c r="E2" t="n">
-        <v>20.67028595500831</v>
+        <v>3.35892146768885</v>
       </c>
       <c r="F2" t="n">
-        <v>19.08717325355552</v>
+        <v>3.101665653702772</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.11500387195087</v>
+        <v>4.893688129192015</v>
       </c>
       <c r="D3" t="n">
-        <v>30.05135029015642</v>
+        <v>4.883344422150418</v>
       </c>
       <c r="E3" t="n">
-        <v>20.67028595500831</v>
+        <v>3.35892146768885</v>
       </c>
       <c r="F3" t="n">
-        <v>19.08717325355552</v>
+        <v>3.101665653702772</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>92.43499634544654</v>
+        <v>15.02068690613506</v>
       </c>
       <c r="D4" t="n">
-        <v>87.82764054922825</v>
+        <v>14.27199158924959</v>
       </c>
       <c r="E4" t="n">
-        <v>20.67028595500831</v>
+        <v>3.35892146768885</v>
       </c>
       <c r="F4" t="n">
-        <v>19.08717325355552</v>
+        <v>3.101665653702772</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.90309016958708</v>
+        <v>4.046752152557901</v>
       </c>
       <c r="D5" t="n">
-        <v>26.04937728432973</v>
+        <v>4.233023808703581</v>
       </c>
       <c r="E5" t="n">
-        <v>20.67028595500831</v>
+        <v>3.35892146768885</v>
       </c>
       <c r="F5" t="n">
-        <v>19.08717325355552</v>
+        <v>3.101665653702772</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>65.86404932758963</v>
+        <v>10.70290801573331</v>
       </c>
       <c r="D6" t="n">
-        <v>62.28964600958975</v>
+        <v>10.12206747655833</v>
       </c>
       <c r="E6" t="n">
-        <v>20.67028595500831</v>
+        <v>3.35892146768885</v>
       </c>
       <c r="F6" t="n">
-        <v>19.08717325355552</v>
+        <v>3.101665653702772</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.0448807642915</v>
+        <v>6.832293124197369</v>
       </c>
       <c r="D7" t="n">
-        <v>39.71352370055352</v>
+        <v>6.453447601339947</v>
       </c>
       <c r="E7" t="n">
-        <v>20.67028595500831</v>
+        <v>3.35892146768885</v>
       </c>
       <c r="F7" t="n">
-        <v>19.08717325355552</v>
+        <v>3.101665653702772</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>48.10799644881757</v>
+        <v>7.817549422932855</v>
       </c>
       <c r="D8" t="n">
-        <v>47.95599113155581</v>
+        <v>7.79284855887782</v>
       </c>
       <c r="E8" t="n">
-        <v>20.67028595500831</v>
+        <v>3.35892146768885</v>
       </c>
       <c r="F8" t="n">
-        <v>19.08717325355552</v>
+        <v>3.101665653702772</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.83534246245379</v>
+        <v>5.173243150148741</v>
       </c>
       <c r="D9" t="n">
-        <v>31.63936698765985</v>
+        <v>5.141397135494725</v>
       </c>
       <c r="E9" t="n">
-        <v>20.67028595500831</v>
+        <v>3.35892146768885</v>
       </c>
       <c r="F9" t="n">
-        <v>19.08717325355552</v>
+        <v>3.101665653702772</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.13225258447402</v>
+        <v>7.821491044977029</v>
       </c>
       <c r="D10" t="n">
-        <v>48.37102777205368</v>
+        <v>7.860292012958723</v>
       </c>
       <c r="E10" t="n">
-        <v>20.67028595500831</v>
+        <v>3.35892146768885</v>
       </c>
       <c r="F10" t="n">
-        <v>19.08717325355552</v>
+        <v>3.101665653702772</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
